--- a/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIN IVA, por comensal: medio entrante, una pizza, 1,3 bebidas y algún postre o café, unos 22 € con IVA en sala. La Margherita de la carta del caso cuesta 10 € con IVA, en la parte baja de la mediana de 10,90 € de 14 pizzerías de Madrid, Barcelona, Valencia, Marbella y Tenerife (octubre de 2026). El precio con IVA está en la fila «PVP equivalente con IVA» de abajo</t>
+          <t>SIN IVA, por comensal: medio entrante, una pizza, 1,3 bebidas y algún postre o café, unos 22 € con IVA en sala. La Margherita de la carta del caso cuesta 10 € con IVA, algo por debajo de la mediana de 10,90 € de 14 pizzerías de Madrid, Barcelona, Valencia, Marbella y Tenerife (octubre de 2026). El precio con IVA está en la fila «PVP equivalente con IVA» de abajo</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por la bebida que sale para llevar o a domicilio (es una entrega de bienes). El alcohol servido en sala va al reducido, como fija la línea de bebida del P&amp;L. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo. En las compras, el libro manda al general la parte de la bebida que declara la celda «Bebida que compras al 21 %» de esta hoja: la cerveza, el vino y los refrescos con azúcares añadidos, cuya factura va al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992)</t>
+          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por la bebida que sale para llevar o a domicilio (es una entrega de bienes). El alcohol servido en sala va al reducido, como fija la línea de bebida del P&amp;L. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo. En las compras, el libro manda al general la parte de la bebida que declara la celda «Bebida que compras al 21 %» de esta hoja: la cerveza, el vino y los refrescos con azúcares o edulcorantes añadidos, cuya factura va al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992)</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bebida que compras al 21 % (alcohol y refrescos con azúcar) sobre el total de bebida</t>
+          <t>Bebida que compras al 21 % (alcohol y refrescos azucarados o edulcorados) sobre el total de bebida</t>
         </is>
       </c>
       <c r="B62" s="64" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sólo mueve el IVA que SOPORTAS al comprar la bebida: la cerveza, el vino y los refrescos con azúcares añadidos te los facturan al 21 % y el agua y el café, al 10 %; con un 80 % sale un 18,8 %. El IVA que REPERCUTES lo fija la línea de bebida del P&amp;L (columna H)</t>
+          <t>Sólo mueve el IVA que SOPORTAS al comprar la bebida: la cerveza, el vino y los refrescos con azúcares o edulcorantes añadidos te los facturan al 21 % y el agua y el café, al 10 %; con un 80 % sale un 18,8 %. El IVA que REPERCUTES lo fija la línea de bebida del P&amp;L (columna H)</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SIN EFECTO en este libro: el IVA que repercute la bebida lo fija su línea del P&amp;L. En sala, todo al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992); para llevar o a domicilio, el alcohol y los refrescos con azúcares añadidos, al 21 %, en la columna H de esa línea</t>
+          <t>SIN EFECTO en este libro: el IVA que repercute la bebida lo fija su línea del P&amp;L. En sala, todo al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992); para llevar o a domicilio, el alcohol y los refrescos con azúcares o edulcorantes añadidos, al 21 %, en la columna H de esa línea</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>Conducto exclusivo hasta la cubierta y, con leña, filtro de partículas: Madrid pide superar en 1 m lo que haya en 15 m (Ordenanza 4/2021). Nadie pública precio por metro: pide oferta con tu proyecto</t>
+          <t>Conducto exclusivo hasta la cubierta y, con leña, filtro de partículas: Madrid pide superar en 1 m lo que haya en 15 m (Ordenanza 4/2021). Ningún fabricante da precio por metro: pide oferta con tu proyecto</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Bebida de sala y la que sale con los pedidos · La columna H es la parte de la bebida que sale del local y va al 21 % (alcohol y refrescos con azúcares añadidos: art. 91.Uno.1.1.º de la Ley 37/1992); el agua, el café y los zumos sin azúcar, y toda la bebida en sala, al 10 %. Un 7 % = un 1,3 % de las ventas</t>
+          <t>Bebida de sala y la que sale con los pedidos · La columna H es la parte de la bebida que sale del local y va al 21 % (alcohol y refrescos con azúcares o edulcorantes añadidos: art. 91.Uno.1.1.º de la Ley 37/1992); el agua, el café y los zumos sin azúcares ni edulcorantes añadidos, y toda la bebida en sala, al 10 %. Un 7 % = un 1,3 % de las ventas</t>
         </is>
       </c>
       <c r="G11" s="68">
@@ -6533,7 +6533,7 @@
     <row r="8" ht="225" customHeight="1">
       <c r="A8" s="48" t="inlineStr">
         <is>
-          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide por el tipo que le corresponda: entre 1,10 en sala (comida y bebida, alcohol incluido: art. 91.Uno.2.2.º de la Ley 37/1992 del IVA) y, cuando se venden para llevar, los alimentos —las pizzas incluidas—, que son productos alimenticios al tipo reducido por el art. 91.Uno.1.1.º; y entre 1,21 el tipo general, que en hostelería sólo alcanza a lo que sale del local como entrega de bienes excluida del reducido: el alcohol y los refrescos o zumos con azúcares añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica a la parte de la bebida que declara la columna H de su línea en el P&amp;L. El tipo de cada línea de venta está en la columna «Tipo de IVA de la línea» del P&amp;L y de ahí salen los cobros, el IVA repercutido y el PVP equivalente. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
+          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide por el tipo que le corresponda: entre 1,10 en sala (comida y bebida, alcohol incluido: art. 91.Uno.2.2.º de la Ley 37/1992 del IVA) y, cuando se venden para llevar, los alimentos —las pizzas incluidas—, que son productos alimenticios al tipo reducido por el art. 91.Uno.1.1.º; y entre 1,21 el tipo general, que en hostelería sólo alcanza a lo que sale del local como entrega de bienes excluida del reducido: el alcohol y los refrescos o zumos con azúcares o edulcorantes añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica a la parte de la bebida que declara la columna H de su línea en el P&amp;L. El tipo de cada línea de venta está en la columna «Tipo de IVA de la línea» del P&amp;L y de ahí salen los cobros, el IVA repercutido y el PVP equivalente. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
         </is>
       </c>
       <c r="B8" s="29" t="n"/>
@@ -6574,10 +6574,10 @@
       <c r="D11" s="29" t="n"/>
       <c r="E11" s="29" t="n"/>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="135" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
         <is>
-          <t>8. El plan de negocio en Word de este pack cita las cifras de este Excel: si cambias una celda verde, el Excel manda. La calculadora de masa y escandallo del pack va aparte: el coste de cada pizza que te dé es el que tienes que llevar a la celda de coste de la comida de la hoja de Supuestos.</t>
+          <t>8. El plan de negocio en Word de este pack cita las cifras de este Excel: si cambias una celda verde, el Excel manda. La calculadora de masa y escandallo del pack va aparte y sirve para ESCANDALLAR cada pizza: no copies el food cost de una pizza en la hoja de Supuestos. La celda «Coste de mercancía sobre las ventas de COMIDA» es la media ponderada de TODA la carta (pizzas, entrantes y postres, cada uno por lo que vende) más la merma, y por eso sale bastante más alta que el food cost de la Margherita. Con los escandallos de tu carta, comprueba que esa media cuadra.</t>
         </is>
       </c>
       <c r="B12" s="29" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="E35" s="29" t="n"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
         <is>
           <t>Coste de la Margherita</t>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>Harina, fior di latte, tomate y aceite: unos 1,36 € con merma sobre 9,09 € sin IVA. Con búfala, burrata o embutido italiano, un 20-28 %</t>
+          <t>Masa, tomate, fior di latte, aceite y albahaca: unos 1,32 € con merma sobre 9,09 € sin IVA, según la calculadora del pack. Con búfala, burrata o embutido italiano, un 20-28 %</t>
         </is>
       </c>
       <c r="E36" s="29" t="n"/>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="E41" s="29" t="n"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="29" t="inlineStr">
         <is>
           <t>IVA de la pizza</t>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="D42" s="48" t="inlineStr">
         <is>
-          <t>En sala, para llevar y a domicilio. El alcohol y los refrescos con azúcares añadidos que salen del local, al 21 %</t>
+          <t>En sala, para llevar y a domicilio. El alcohol y los refrescos con azúcares o edulcorantes añadidos que salen del local, al 21 %</t>
         </is>
       </c>
       <c r="E42" s="29" t="n"/>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="O16" s="29" t="inlineStr">
         <is>
-          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); la parte de la bebida que sale para llevar o a domicilio y declara la columna H de su línea (alcohol y refrescos con azúcares añadidos), al general (art. 91.Uno.1.1.º)</t>
+          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); la parte de la bebida que sale para llevar o a domicilio y declara la columna H de su línea (alcohol y refrescos con azúcares o edulcorantes añadidos), al general (art. 91.Uno.1.1.º)</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
         <v>0.03103306349785405</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Chimenea de doble pared hasta cubierta, filtro de partículas y bancada del horno, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización y extracción), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Chimenea de doble pared hasta cubierta, filtro de "&amp;"partículas y bancada del horno, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización y extracción), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una "&amp;"reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Chimenea de doble pared hasta cubierta, filtro de partículas y bancada del horno, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización y extracción), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E32" s="29" t="n"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="26" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos, formación de pizzaiolo y lanzamiento, Stock inicial de harina, tomate, quesos, bebida, leña y cajas, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos, formación de pizzaiolo y lanzamiento, Stock inicial de harina, tomate, quesos, bebida, leña y cajas, Fianza "&amp;"del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos, formación de pizzaiolo y lanzamiento, Stock inicial de harina, tomate, quesos, bebida, leña y cajas, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 77703 € de los 194953 € de inversión.</v>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>

--- a/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-pizzeria/plan-financiero-pizzeria.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
         <v>0.03103306349785405</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Chimenea de doble pared hasta cubierta, filtro de partículas y bancada del horno, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización y extracción), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Chimenea de doble pared hasta cubierta, filtro de "&amp;"partículas y bancada del horno, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización y extracción), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una "&amp;"reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Chimenea de doble pared hasta cubierta, filtro de partículas y bancada del horno, Instalación eléctrica trifásica, cuadro y boletín y Fontanería, separador de grasas, climatización y extracción), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E32" s="29" t="n"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="26" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos, formación de pizzaiolo y lanzamiento, Stock inicial de harina, tomate, quesos, bebida, leña y cajas, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos, formación de pizzaiolo y lanzamiento, Stock inicial de harina, tomate, quesos, bebida, leña y cajas, Fianza "&amp;"del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos, formación de pizzaiolo y lanzamiento, Stock inicial de harina, tomate, quesos, bebida, leña y cajas, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 77703 € de los 194953 € de inversión.</v>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
